--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_antofagasta.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:40</t>
+    <t xml:space="preserve">2026-09-09 20:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_antofagasta.xlsx
@@ -27,24 +27,24 @@
     <t xml:space="preserve">Antofagasta</t>
   </si>
   <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calama</t>
   </si>
   <si>
-    <t xml:space="preserve">Mejillones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ollagüe</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:44</t>
+    <t xml:space="preserve">2026-09-18 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -477,7 +477,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.41</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="4">
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.35</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.44</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +509,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.56</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="9">
